--- a/public/ITNOW/ITNOW_History.xlsx
+++ b/public/ITNOW/ITNOW_History.xlsx
@@ -1406,16 +1406,16 @@
         <v>2026</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0023</v>
+        <v>0.0013</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0053</v>
+        <v>0.0042</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0015</v>
+        <v>-0.0069</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0133</v>
+        <v>0.0176</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1429,7 +1429,42 @@
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="C8" s="8" t="n"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.004500000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="C9" s="8" t="n"/>
